--- a/figures/tp_sl_grid_63.xlsx
+++ b/figures/tp_sl_grid_63.xlsx
@@ -481,22 +481,22 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5010462453609875</v>
+        <v>0.4997435144825165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01672347537704314</v>
+        <v>0.008613524330463073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4822302792619693</v>
+        <v>0.4916429611870204</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0188159660990182</v>
+        <v>0.008100553295496027</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7663729227398465</v>
+        <v>0.736672290617461</v>
       </c>
     </row>
     <row r="3">
@@ -510,22 +510,22 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5755007501381834</v>
+        <v>0.5763215862051939</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02494867475587608</v>
+        <v>0.01573751244709129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3995505751059406</v>
+        <v>0.4079409013477148</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1759501750322428</v>
+        <v>0.1683806848574791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7766102360140705</v>
+        <v>0.7487155689596616</v>
       </c>
     </row>
     <row r="4">
@@ -539,22 +539,22 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4183303503276919</v>
+        <v>0.4147768575997893</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02538296528307846</v>
+        <v>0.01606394856025215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5562866843892296</v>
+        <v>0.5691591938399585</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1379563340615376</v>
+        <v>0.1543823362401692</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7840632406164884</v>
+        <v>0.7521480484137399</v>
       </c>
     </row>
     <row r="5">
@@ -568,22 +568,22 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6246808622641012</v>
+        <v>0.6283511135860516</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03780959650461927</v>
+        <v>0.02747823987842312</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3375095412312795</v>
+        <v>0.3441706465355253</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2871713210328218</v>
+        <v>0.2841804670505262</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7843448953529844</v>
+        <v>0.7578324255548248</v>
       </c>
     </row>
     <row r="6">
@@ -597,22 +597,22 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3567170268207301</v>
+        <v>0.3514893990558041</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03893151369989208</v>
+        <v>0.02864408313971191</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6043514594793777</v>
+        <v>0.619866517804484</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2476344326586476</v>
+        <v>0.2683771187486799</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7984291560637808</v>
+        <v>0.7657275748104884</v>
       </c>
     </row>
     <row r="7">
@@ -626,22 +626,22 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4893105308872687</v>
+        <v>0.4881015408333173</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04108980601689785</v>
+        <v>0.0305834976943735</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4695996630958335</v>
+        <v>0.4813149614723092</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01971086779143527</v>
+        <v>0.006786579361008127</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8358555749991843</v>
+        <v>0.8086892069748355</v>
       </c>
     </row>
     <row r="8">
@@ -655,22 +655,22 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6579962098281262</v>
+        <v>0.6629807731872509</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05555957676414076</v>
+        <v>0.044965888797755</v>
       </c>
       <c r="F8" t="n">
-        <v>0.286444213407733</v>
+        <v>0.2920533380149941</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3715519964203932</v>
+        <v>0.3709274351722568</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7941079835532869</v>
+        <v>0.7714334924359201</v>
       </c>
     </row>
     <row r="9">
@@ -684,22 +684,22 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3059510962545732</v>
+        <v>0.3004913000661102</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05693483010028163</v>
+        <v>0.0453499312838266</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6371140736451452</v>
+        <v>0.6541587686500633</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3311629773905719</v>
+        <v>0.3536674685839531</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8127288332714953</v>
+        <v>0.7792030820838424</v>
       </c>
     </row>
     <row r="10">
@@ -713,22 +713,22 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5367830916221409</v>
+        <v>0.5385263192545187</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06383083725949518</v>
+        <v>0.05176892712245194</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3993860711183639</v>
+        <v>0.4097047536230294</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.137397020503777</v>
+        <v>0.1288215656314893</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8761645709407195</v>
+        <v>0.8521772367376907</v>
       </c>
     </row>
     <row r="11">
@@ -742,138 +742,138 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4211828494722712</v>
+        <v>0.4180631640163163</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06390979917353197</v>
+        <v>0.05226818235434503</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5149073513541969</v>
+        <v>0.5296686536293387</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09372450188192566</v>
+        <v>0.1116054896130224</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8817410262689359</v>
+        <v>0.8554713675507911</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
         <v>2</v>
       </c>
-      <c r="C12" t="n">
-        <v>6</v>
-      </c>
       <c r="D12" t="n">
-        <v>0.680191087831969</v>
+        <v>0.2567406314207103</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07647132366488564</v>
+        <v>0.06581939579144298</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2433375885031453</v>
+        <v>0.6774399727878467</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4368534993288237</v>
+        <v>0.4206993413671364</v>
       </c>
       <c r="I12" t="n">
-        <v>0.802638924849483</v>
+        <v>0.7919898634983127</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
         <v>6</v>
       </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
       <c r="D13" t="n">
-        <v>0.2624759824178138</v>
+        <v>0.6865500091895881</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07895204379754166</v>
+        <v>0.06727327091728548</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6585719737846445</v>
+        <v>0.2461767198931264</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3960959913668307</v>
+        <v>0.4403732892964616</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8266125485942868</v>
+        <v>0.7848324550779964</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="C14" t="n">
-        <v>5</v>
-      </c>
       <c r="D14" t="n">
-        <v>0.5687396362487827</v>
+        <v>0.3576752262421717</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09175045403100571</v>
+        <v>0.07965864109309465</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3395099097202116</v>
+        <v>0.5626661326647336</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.229229726528571</v>
+        <v>0.204990906422562</v>
       </c>
       <c r="I14" t="n">
-        <v>0.906877318382286</v>
+        <v>0.8928450915462558</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" t="n">
-        <v>3</v>
-      </c>
       <c r="D15" t="n">
-        <v>0.3615995051720053</v>
+        <v>0.5713921265804034</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09225712631274183</v>
+        <v>0.08040203761970467</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5461433685152528</v>
+        <v>0.3482058357998919</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1845438633432475</v>
+        <v>0.2231862907805115</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9180382671174958</v>
+        <v>0.8898109271704691</v>
       </c>
     </row>
     <row r="16">
@@ -887,370 +887,370 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4637170005000921</v>
+        <v>0.4627876546799692</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09666912325954781</v>
+        <v>0.0841409655376732</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4396138762403601</v>
+        <v>0.4530713797823576</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02410312425973204</v>
+        <v>0.009716274897611565</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9435216762878962</v>
+        <v>0.9235419075478299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
-        <v>7</v>
-      </c>
       <c r="D17" t="n">
-        <v>0.6946509883399573</v>
+        <v>0.2184214207926088</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09987366093754113</v>
+        <v>0.08893601029233862</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2054753507225015</v>
+        <v>0.6926425689150525</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4891756376174558</v>
+        <v>0.4742211481224436</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8083371785921947</v>
+        <v>0.8018684594817458</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
         <v>7</v>
       </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
       <c r="D18" t="n">
-        <v>0.22366949174848</v>
+        <v>0.7016895126226536</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1036473824125497</v>
+        <v>0.09266945188907756</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6726831258389704</v>
+        <v>0.2056410354882689</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4490136340904904</v>
+        <v>0.4960484771343847</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8366140744107964</v>
+        <v>0.794264487245202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
         <v>3</v>
       </c>
-      <c r="C19" t="n">
-        <v>6</v>
-      </c>
       <c r="D19" t="n">
-        <v>0.5893848866896534</v>
+        <v>0.3049955697956071</v>
       </c>
       <c r="E19" t="n">
-        <v>0.122723264811939</v>
+        <v>0.1106124654704658</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2878918484984076</v>
+        <v>0.5843919647339272</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3014930381912458</v>
+        <v>0.2793963949383201</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9275196893245321</v>
+        <v>0.9196330201474527</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3096228252572842</v>
+        <v>0.1846476273032262</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1242564419761535</v>
+        <v>0.1134406640643216</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5661207327665623</v>
+        <v>0.7019117086324521</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.256497907509278</v>
+        <v>0.5172640813292259</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9442204856059877</v>
+        <v>0.8072671524144095</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
         <v>6</v>
       </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>8</v>
-      </c>
       <c r="D21" t="n">
-        <v>0.7031624246571737</v>
+        <v>0.5936144707208751</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1244604269207486</v>
+        <v>0.1135942810587503</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1723771484220777</v>
+        <v>0.2927912482203746</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.530785276235096</v>
+        <v>0.3008232225005006</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8100286227728365</v>
+        <v>0.916300480919498</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
       <c r="D22" t="n">
-        <v>0.1897388992709183</v>
+        <v>0.71100254290989</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1283822019845761</v>
+        <v>0.1179833380424257</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6818788987445056</v>
+        <v>0.1710141190476843</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4921399994735872</v>
+        <v>0.5399884238622056</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8399955770486687</v>
+        <v>0.7966761178749122</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
       <c r="D23" t="n">
-        <v>0.4923275340194246</v>
+        <v>0.3961069064554799</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1338963756481457</v>
+        <v>0.1219060577215857</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3737760903324296</v>
+        <v>0.4819870358229345</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.118551443686995</v>
+        <v>0.08588012936745459</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9859251508983532</v>
+        <v>0.9751475079657879</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
         <v>5</v>
       </c>
-      <c r="C24" t="n">
-        <v>4</v>
-      </c>
       <c r="D24" t="n">
-        <v>0.3985503908614745</v>
+        <v>0.4921422164189135</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1344918800831732</v>
+        <v>0.1228634207761499</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4669577290553523</v>
+        <v>0.3849943628049366</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06840733819387784</v>
+        <v>0.1071478536139769</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9920555701891005</v>
+        <v>0.9740155701582109</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
         <v>3</v>
       </c>
-      <c r="C25" t="n">
-        <v>7</v>
-      </c>
       <c r="D25" t="n">
-        <v>0.6024794041007554</v>
+        <v>0.2586334122449204</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1556207722475193</v>
+        <v>0.1430475965798274</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2418998236517253</v>
+        <v>0.5983189911752523</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.36057958044903</v>
+        <v>0.339685578930332</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9380957517726439</v>
+        <v>0.9352437541366336</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
         <v>7</v>
       </c>
-      <c r="C26" t="n">
-        <v>3</v>
-      </c>
       <c r="D26" t="n">
-        <v>0.262693127681415</v>
+        <v>0.6076265351412591</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1578678967178165</v>
+        <v>0.1485860378611028</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5794389756007685</v>
+        <v>0.2437874269976381</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3167458479193535</v>
+        <v>0.363839108143621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9587804837497687</v>
+        <v>0.9301050871855678</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="n">
         <v>4</v>
       </c>
-      <c r="C27" t="n">
-        <v>6</v>
-      </c>
       <c r="D27" t="n">
-        <v>0.5103440107388203</v>
+        <v>0.3369698499216828</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1734233937830653</v>
+        <v>0.1621756555468079</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3162325954781144</v>
+        <v>0.5008544945315093</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1941114152607059</v>
+        <v>0.1638846446098265</v>
       </c>
       <c r="I27" t="n">
-        <v>1.01120576579368</v>
+        <v>1.007863309448292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
         <v>6</v>
       </c>
-      <c r="C28" t="n">
-        <v>4</v>
-      </c>
       <c r="D28" t="n">
-        <v>0.3403752006948648</v>
+        <v>0.511528132483685</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1748973495117522</v>
+        <v>0.1652425091141511</v>
       </c>
       <c r="F28" t="n">
-        <v>0.484727449793383</v>
+        <v>0.3232293584021638</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1443522490985182</v>
+        <v>0.1882987740815212</v>
       </c>
       <c r="I28" t="n">
-        <v>1.022792329213086</v>
+        <v>1.005450158648118</v>
       </c>
     </row>
     <row r="29">
@@ -1264,312 +1264,312 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4228673703050562</v>
+        <v>0.4211217881018152</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1800660648014108</v>
+        <v>0.1695026375489311</v>
       </c>
       <c r="F29" t="n">
-        <v>0.397066564893533</v>
+        <v>0.4093755743492537</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.02580080541152313</v>
+        <v>0.01174621375256146</v>
       </c>
       <c r="I29" t="n">
-        <v>1.039422538537982</v>
+        <v>1.030670536972532</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" t="n">
         <v>3</v>
       </c>
-      <c r="C30" t="n">
-        <v>8</v>
-      </c>
       <c r="D30" t="n">
-        <v>0.610178190719343</v>
+        <v>0.2176176747324733</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1877319506224831</v>
+        <v>0.1756281152017732</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2020898586581739</v>
+        <v>0.6067542100657536</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4080883320611691</v>
+        <v>0.3891365353332803</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9386077233641308</v>
+        <v>0.9405090193826404</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="n">
         <v>8</v>
       </c>
-      <c r="C31" t="n">
-        <v>3</v>
-      </c>
       <c r="D31" t="n">
-        <v>0.2218073066091122</v>
+        <v>0.6159108801979465</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1904857473745163</v>
+        <v>0.181945614097651</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5877069460163714</v>
+        <v>0.2021435057044025</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3658996394072592</v>
+        <v>0.4137673744935439</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9622711583378832</v>
+        <v>0.9317294853882117</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
         <v>4</v>
       </c>
-      <c r="C32" t="n">
-        <v>7</v>
-      </c>
       <c r="D32" t="n">
-        <v>0.5215401521332877</v>
+        <v>0.2849046614528327</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2135788171505277</v>
+        <v>0.2024397670508006</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2648810307161846</v>
+        <v>0.5126555714963666</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2566591214171032</v>
+        <v>0.2277509100435339</v>
       </c>
       <c r="I32" t="n">
-        <v>1.021106328563752</v>
+        <v>1.023617493953285</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
         <v>7</v>
       </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
       <c r="D33" t="n">
-        <v>0.2880037112099597</v>
+        <v>0.5232578872725577</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2159739952096439</v>
+        <v>0.2080495305080608</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4960222935803964</v>
+        <v>0.2686925822193815</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2080185823704367</v>
+        <v>0.2545653050531762</v>
       </c>
       <c r="I33" t="n">
-        <v>1.037281259650624</v>
+        <v>1.018649919781353</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
         <v>5</v>
       </c>
-      <c r="C34" t="n">
-        <v>6</v>
-      </c>
       <c r="D34" t="n">
-        <v>0.4380445081988787</v>
+        <v>0.3573295880047073</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2267029452793936</v>
+        <v>0.217527150432185</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3352525465217277</v>
+        <v>0.4251432615631078</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.102791961677151</v>
+        <v>0.06781367355840051</v>
       </c>
       <c r="I34" t="n">
-        <v>1.06441817918731</v>
+        <v>1.063186885184956</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
         <v>6</v>
       </c>
-      <c r="C35" t="n">
-        <v>5</v>
-      </c>
       <c r="D35" t="n">
-        <v>0.3605532598110178</v>
+        <v>0.4371967093045265</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2276077172110652</v>
+        <v>0.2197052199603339</v>
       </c>
       <c r="F35" t="n">
-        <v>0.411839022977917</v>
+        <v>0.3430980707351396</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05128576316689915</v>
+        <v>0.09409863856938688</v>
       </c>
       <c r="I35" t="n">
-        <v>1.070047147745003</v>
+        <v>1.06170605408241</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
         <v>4</v>
       </c>
-      <c r="C36" t="n">
-        <v>8</v>
-      </c>
       <c r="D36" t="n">
-        <v>0.5281170215566026</v>
+        <v>0.238921060066988</v>
       </c>
       <c r="E36" t="n">
-        <v>0.251191008870055</v>
+        <v>0.2410744411496037</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2206919695733424</v>
+        <v>0.5200044987834083</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3074250519832601</v>
+        <v>0.2810834387164203</v>
       </c>
       <c r="I36" t="n">
-        <v>1.017663261466621</v>
+        <v>1.02504930198237</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
         <v>8</v>
       </c>
-      <c r="C37" t="n">
-        <v>4</v>
-      </c>
       <c r="D37" t="n">
-        <v>0.2427519543073724</v>
+        <v>0.5303407279799639</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2541849814439502</v>
+        <v>0.2472849567815045</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5030630642486774</v>
+        <v>0.2223743152385315</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.260311109941305</v>
+        <v>0.3079664127414323</v>
       </c>
       <c r="I37" t="n">
-        <v>1.037447317227535</v>
+        <v>1.016186988636728</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="n">
         <v>5</v>
       </c>
-      <c r="C38" t="n">
-        <v>7</v>
-      </c>
       <c r="D38" t="n">
-        <v>0.4472468612639171</v>
+        <v>0.301454149441904</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2724876951017293</v>
+        <v>0.2637740952370502</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2802654436343537</v>
+        <v>0.4347717553210458</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1669814176295634</v>
+        <v>0.1333176058791418</v>
       </c>
       <c r="I38" t="n">
-        <v>1.070655575809511</v>
+        <v>1.075142918451594</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
         <v>7</v>
       </c>
-      <c r="C39" t="n">
-        <v>5</v>
-      </c>
       <c r="D39" t="n">
-        <v>0.3046219040349538</v>
+        <v>0.446751137725865</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2741755060142658</v>
+        <v>0.2684841020126569</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4212025899507804</v>
+        <v>0.2847647602614781</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1165806859158266</v>
+        <v>0.1619863774643869</v>
       </c>
       <c r="I39" t="n">
-        <v>1.081067832972855</v>
+        <v>1.070708832308076</v>
       </c>
     </row>
     <row r="40">
@@ -1583,196 +1583,196 @@
         <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3728746084805096</v>
+        <v>0.3703184535157718</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2797456110336115</v>
+        <v>0.2737976041235191</v>
       </c>
       <c r="F40" t="n">
-        <v>0.347379780485879</v>
+        <v>0.3558839423607091</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0254948279946306</v>
+        <v>0.01443451115506267</v>
       </c>
       <c r="I40" t="n">
-        <v>1.091503878110687</v>
+        <v>1.090221220619231</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" t="n">
         <v>5</v>
       </c>
-      <c r="C41" t="n">
-        <v>8</v>
-      </c>
       <c r="D41" t="n">
-        <v>0.4526195614981707</v>
+        <v>0.2524201534524048</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3142157765904245</v>
+        <v>0.3067703947133809</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2331646619114047</v>
+        <v>0.4408094518342143</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.219454899586766</v>
+        <v>0.1883892983818095</v>
       </c>
       <c r="I41" t="n">
-        <v>1.062043051806503</v>
+        <v>1.071079582362139</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
         <v>8</v>
       </c>
-      <c r="C42" t="n">
-        <v>5</v>
-      </c>
       <c r="D42" t="n">
-        <v>0.2564288158344958</v>
+        <v>0.4525721245504645</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3164201300239518</v>
+        <v>0.3122951201915823</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4271510541415524</v>
+        <v>0.2351327552579531</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1707222383070566</v>
+        <v>0.2174393692925114</v>
       </c>
       <c r="I42" t="n">
-        <v>1.076416949911959</v>
+        <v>1.062633348766715</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" t="n">
         <v>6</v>
       </c>
-      <c r="C43" t="n">
-        <v>7</v>
-      </c>
       <c r="D43" t="n">
-        <v>0.3804944331850604</v>
+        <v>0.311839755529526</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3293764640854894</v>
+        <v>0.3244582943575929</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2901291027294501</v>
+        <v>0.363701950112881</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.09036533045561029</v>
+        <v>0.051862194583355</v>
       </c>
       <c r="I43" t="n">
-        <v>1.092470144243982</v>
+        <v>1.096441535673218</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B44" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" t="n">
         <v>7</v>
       </c>
-      <c r="C44" t="n">
-        <v>6</v>
-      </c>
       <c r="D44" t="n">
-        <v>0.3146369067986208</v>
+        <v>0.3780130190402778</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3302911062564157</v>
+        <v>0.3271246464751758</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3550719869449636</v>
+        <v>0.2948623344845464</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.04043508014634278</v>
+        <v>0.08315068455573144</v>
       </c>
       <c r="I44" t="n">
-        <v>1.097370010554734</v>
+        <v>1.093374443570447</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="n">
         <v>6</v>
       </c>
-      <c r="C45" t="n">
-        <v>8</v>
-      </c>
       <c r="D45" t="n">
-        <v>0.3848439186165873</v>
+        <v>0.2605645973177376</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3742070907798805</v>
+        <v>0.3707518728929097</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2409489906035322</v>
+        <v>0.3686835297893527</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1438949280130551</v>
+        <v>0.1081189324716151</v>
       </c>
       <c r="I45" t="n">
-        <v>1.078230876594967</v>
+        <v>1.086181308950678</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="n">
         <v>8</v>
       </c>
-      <c r="C46" t="n">
-        <v>6</v>
-      </c>
       <c r="D46" t="n">
-        <v>0.2644467401889822</v>
+        <v>0.3826791352460478</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3753421682941595</v>
+        <v>0.3744606260441155</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3602110915168584</v>
+        <v>0.2428602387098367</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0957643513278762</v>
+        <v>0.1398188965362111</v>
       </c>
       <c r="I46" t="n">
-        <v>1.087347892630482</v>
+        <v>1.079119183602584</v>
       </c>
     </row>
     <row r="47">
@@ -1786,80 +1786,80 @@
         <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3206084015476535</v>
+        <v>0.3180091237522048</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3830541152317532</v>
+        <v>0.3809536872193404</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2963374832205933</v>
+        <v>0.3010371890284548</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.02427091832706024</v>
+        <v>0.01697193472374997</v>
       </c>
       <c r="I47" t="n">
-        <v>1.09269624830705</v>
+        <v>1.093386593551202</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B48" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" t="n">
         <v>7</v>
       </c>
-      <c r="C48" t="n">
-        <v>8</v>
-      </c>
       <c r="D48" t="n">
-        <v>0.3240432448082541</v>
+        <v>0.2654035326422398</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4299706524886163</v>
+        <v>0.429603640722768</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2459861027031295</v>
+        <v>0.3049928266349923</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07805714210512463</v>
+        <v>0.03958929399275257</v>
       </c>
       <c r="I48" t="n">
-        <v>1.073059654097734</v>
+        <v>1.077196518879618</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B49" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" t="n">
         <v>8</v>
       </c>
-      <c r="C49" t="n">
-        <v>7</v>
-      </c>
       <c r="D49" t="n">
-        <v>0.2692469665464691</v>
+        <v>0.3216410684061963</v>
       </c>
       <c r="E49" t="n">
-        <v>0.430141736635696</v>
+        <v>0.4306378122745465</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3006112968178349</v>
+        <v>0.2477211193192572</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.03136433027136581</v>
+        <v>0.07391994908693902</v>
       </c>
       <c r="I49" t="n">
-        <v>1.077486902522326</v>
+        <v>1.073333580866863</v>
       </c>
     </row>
     <row r="50">
@@ -1873,22 +1873,22 @@
         <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2720632748137815</v>
+        <v>0.2683030534120803</v>
       </c>
       <c r="E50" t="n">
-        <v>0.478581580817519</v>
+        <v>0.4808897715770156</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2493551443686995</v>
+        <v>0.250807175010904</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.02270813044508202</v>
+        <v>0.01749587840117628</v>
       </c>
       <c r="I50" t="n">
-        <v>1.053154472770665</v>
+        <v>1.05194149639525</v>
       </c>
     </row>
   </sheetData>

--- a/figures/tp_sl_grid_63.xlsx
+++ b/figures/tp_sl_grid_63.xlsx
@@ -481,22 +481,22 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4997435144825165</v>
+        <v>0.5016455792489668</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008613524330463073</v>
+        <v>0.009837977636349806</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4916429611870204</v>
+        <v>0.4885164431146835</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008100553295496027</v>
+        <v>0.01312913613428335</v>
       </c>
       <c r="I2" t="n">
-        <v>0.736672290617461</v>
+        <v>0.7414966543177484</v>
       </c>
     </row>
     <row r="3">
@@ -510,22 +510,22 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5763215862051939</v>
+        <v>0.5781814954740232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01573751244709129</v>
+        <v>0.01725956540480235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4079409013477148</v>
+        <v>0.4045589391211745</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1683806848574791</v>
+        <v>0.1736225563528487</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7487155689596616</v>
+        <v>0.7529388921952491</v>
       </c>
     </row>
     <row r="4">
@@ -539,22 +539,22 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4147768575997893</v>
+        <v>0.4164431146834352</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01606394856025215</v>
+        <v>0.01748269479449276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5691591938399585</v>
+        <v>0.5660741905220721</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1543823362401692</v>
+        <v>0.1496310758386369</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7521480484137399</v>
+        <v>0.7576641768788774</v>
       </c>
     </row>
     <row r="5">
@@ -568,22 +568,22 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6283511135860516</v>
+        <v>0.6298080580136414</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02747823987842312</v>
+        <v>0.02928573239686605</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3441706465355253</v>
+        <v>0.3409062095894926</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2841804670505262</v>
+        <v>0.2889018484241487</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7578324255548248</v>
+        <v>0.7614488741752379</v>
       </c>
     </row>
     <row r="6">
@@ -597,22 +597,22 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3514893990558041</v>
+        <v>0.3535104845457542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02864408313971191</v>
+        <v>0.03029488577296584</v>
       </c>
       <c r="F6" t="n">
-        <v>0.619866517804484</v>
+        <v>0.6161946296812799</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2683771187486799</v>
+        <v>0.2626841451355257</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7657275748104884</v>
+        <v>0.7718862961402437</v>
       </c>
     </row>
     <row r="7">
@@ -626,22 +626,22 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4881015408333173</v>
+        <v>0.4898780395040442</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0305834976943735</v>
+        <v>0.03251350186363752</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4813149614723092</v>
+        <v>0.4776084586323183</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.006786579361008127</v>
+        <v>0.01226958087172597</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8086892069748355</v>
+        <v>0.8139063502677396</v>
       </c>
     </row>
     <row r="8">
@@ -655,22 +655,22 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6629807731872509</v>
+        <v>0.6644514313243236</v>
       </c>
       <c r="E8" t="n">
-        <v>0.044965888797755</v>
+        <v>0.04677096275260529</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2920533380149941</v>
+        <v>0.2887776059230711</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3709274351722568</v>
+        <v>0.3756738254012525</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7714334924359201</v>
+        <v>0.7735493594235809</v>
       </c>
     </row>
     <row r="9">
@@ -684,22 +684,22 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3004913000661102</v>
+        <v>0.3029691422196303</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0453499312838266</v>
+        <v>0.04690027637617587</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6541587686500633</v>
+        <v>0.6501305814041938</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3536674685839531</v>
+        <v>0.3471614391845634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7792030820838424</v>
+        <v>0.7852196338334959</v>
       </c>
     </row>
     <row r="10">
@@ -713,22 +713,22 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5385263192545187</v>
+        <v>0.5401506123380411</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05176892712245194</v>
+        <v>0.05399477674383225</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4097047536230294</v>
+        <v>0.4058546109181267</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1288215656314893</v>
+        <v>0.1342960014199143</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8521772367376907</v>
+        <v>0.8562698777370654</v>
       </c>
     </row>
     <row r="11">
@@ -742,22 +742,22 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4180631640163163</v>
+        <v>0.4202895610943482</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05226818235434503</v>
+        <v>0.05443342883947361</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5296686536293387</v>
+        <v>0.5252770100661781</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1116054896130224</v>
+        <v>0.1049874489718299</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8554713675507911</v>
+        <v>0.8609441753376845</v>
       </c>
     </row>
     <row r="12">
@@ -771,22 +771,22 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2567406314207103</v>
+        <v>0.2594690534749867</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06581939579144298</v>
+        <v>0.06747635589137656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6774399727878467</v>
+        <v>0.6730545906336367</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4206993413671364</v>
+        <v>0.41358553715865</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7919898634983127</v>
+        <v>0.7984508196494817</v>
       </c>
     </row>
     <row r="13">
@@ -800,22 +800,22 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6865500091895881</v>
+        <v>0.6879763685691828</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06727327091728548</v>
+        <v>0.06901797712923756</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2461767198931264</v>
+        <v>0.2430056543015797</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4403732892964616</v>
+        <v>0.4449707142676031</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7848324550779964</v>
+        <v>0.7855884993948006</v>
       </c>
     </row>
     <row r="14">
@@ -829,22 +829,22 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3576752262421717</v>
+        <v>0.3604427089936357</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07965864109309465</v>
+        <v>0.0816957833616471</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5626661326647336</v>
+        <v>0.5578615076447172</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.204990906422562</v>
+        <v>0.1974187986510815</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8928450915462558</v>
+        <v>0.8980243325660962</v>
       </c>
     </row>
     <row r="15">
@@ -858,22 +858,22 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5713921265804034</v>
+        <v>0.5730419128274044</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08040203761970467</v>
+        <v>0.08254773194046502</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3482058357998919</v>
+        <v>0.3444103552321306</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2231862907805115</v>
+        <v>0.2286315575952737</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8898109271704691</v>
+        <v>0.8920873581061092</v>
       </c>
     </row>
     <row r="16">
@@ -887,22 +887,22 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4627876546799692</v>
+        <v>0.464890083419965</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0841409655376732</v>
+        <v>0.08636628717766677</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4530713797823576</v>
+        <v>0.4487436294023682</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009716274897611565</v>
+        <v>0.01614645401759679</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9235419075478299</v>
+        <v>0.9271890757350811</v>
       </c>
     </row>
     <row r="17">
@@ -916,22 +916,22 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2184214207926088</v>
+        <v>0.220877811303532</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08893601029233862</v>
+        <v>0.09087705063515809</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6926425689150525</v>
+        <v>0.6882451380613098</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4742211481224436</v>
+        <v>0.4673673267577778</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8018684594817458</v>
+        <v>0.8086387442549654</v>
       </c>
     </row>
     <row r="18">
@@ -945,22 +945,22 @@
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7016895126226536</v>
+        <v>0.7030350668120389</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09266945188907756</v>
+        <v>0.09449022541139482</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2056410354882689</v>
+        <v>0.2024747077765663</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4960484771343847</v>
+        <v>0.5005603590354726</v>
       </c>
       <c r="I18" t="n">
-        <v>0.794264487245202</v>
+        <v>0.7940207723376027</v>
       </c>
     </row>
     <row r="19">
@@ -974,22 +974,22 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3049955697956071</v>
+        <v>0.3078120642004107</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1106124654704658</v>
+        <v>0.1128476888359238</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5843919647339272</v>
+        <v>0.5793402469636654</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2793963949383201</v>
+        <v>0.2715281827632546</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9196330201474527</v>
+        <v>0.9251278357730937</v>
       </c>
     </row>
     <row r="20">
@@ -1003,22 +1003,22 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1846476273032262</v>
+        <v>0.1869418595806182</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1134406640643216</v>
+        <v>0.1154669236035396</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7019117086324521</v>
+        <v>0.6975912168158422</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5172640813292259</v>
+        <v>0.5106493572352241</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8072671524144095</v>
+        <v>0.8139781806498078</v>
       </c>
     </row>
     <row r="21">
@@ -1032,22 +1032,22 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5936144707208751</v>
+        <v>0.5950835467430716</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1135942810587503</v>
+        <v>0.1157255508506808</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2927912482203746</v>
+        <v>0.2891909024062476</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3008232225005006</v>
+        <v>0.305892644336824</v>
       </c>
       <c r="I21" t="n">
-        <v>0.916300480919498</v>
+        <v>0.9172362116214199</v>
       </c>
     </row>
     <row r="22">
@@ -1061,22 +1061,22 @@
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>0.71100254290989</v>
+        <v>0.7122771875554654</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1179833380424257</v>
+        <v>0.1197241309363828</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1710141190476843</v>
+        <v>0.1679986815081518</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5399884238622056</v>
+        <v>0.5442785060473136</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7966761178749122</v>
+        <v>0.7954653613956588</v>
       </c>
     </row>
     <row r="23">
@@ -1090,22 +1090,22 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3961069064554799</v>
+        <v>0.3985750145794772</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1219060577215857</v>
+        <v>0.1241664342402191</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4819870358229345</v>
+        <v>0.4772585511803037</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08588012936745459</v>
+        <v>0.07868353660082655</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9751475079657879</v>
+        <v>0.9786873249558911</v>
       </c>
     </row>
     <row r="24">
@@ -1119,22 +1119,22 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4921422164189135</v>
+        <v>0.4941428535206268</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1228634207761499</v>
+        <v>0.1250767007277061</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3849943628049366</v>
+        <v>0.3807804457516671</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1071478536139769</v>
+        <v>0.1133624077689597</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9740155701582109</v>
+        <v>0.9760052215900753</v>
       </c>
     </row>
     <row r="25">
@@ -1148,22 +1148,22 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2586334122449204</v>
+        <v>0.2611349172139253</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1430475965798274</v>
+        <v>0.1455767134055123</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5983189911752523</v>
+        <v>0.5932883693805624</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.339685578930332</v>
+        <v>0.3321534521666371</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9352437541366336</v>
+        <v>0.9409053348631551</v>
       </c>
     </row>
     <row r="26">
@@ -1177,22 +1177,22 @@
         <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6076265351412591</v>
+        <v>0.6090037779862573</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1485860378611028</v>
+        <v>0.1507188316133776</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2437874269976381</v>
+        <v>0.2402773904003651</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.363839108143621</v>
+        <v>0.3687263875858922</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9301050871855678</v>
+        <v>0.9298611318868002</v>
       </c>
     </row>
     <row r="27">
@@ -1206,22 +1206,22 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3369698499216828</v>
+        <v>0.3394761530464768</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1621756555468079</v>
+        <v>0.1645604604579224</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5008544945315093</v>
+        <v>0.4959633864956008</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1638846446098265</v>
+        <v>0.156487233449124</v>
       </c>
       <c r="I27" t="n">
-        <v>1.007863309448292</v>
+        <v>1.011495096908847</v>
       </c>
     </row>
     <row r="28">
@@ -1235,22 +1235,22 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.511528132483685</v>
+        <v>0.5133598722077132</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1652425091141511</v>
+        <v>0.1673647911965314</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3232293584021638</v>
+        <v>0.3192753365957555</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1882987740815212</v>
+        <v>0.1940845356119577</v>
       </c>
       <c r="I28" t="n">
-        <v>1.005450158648118</v>
+        <v>1.005992126805133</v>
       </c>
     </row>
     <row r="29">
@@ -1264,22 +1264,22 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4211217881018152</v>
+        <v>0.423403230305028</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1695026375489311</v>
+        <v>0.1717234209792338</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4093755743492537</v>
+        <v>0.4048733487157382</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01174621375256146</v>
+        <v>0.01852988158928981</v>
       </c>
       <c r="I29" t="n">
-        <v>1.030670536972532</v>
+        <v>1.032518702888822</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2176176747324733</v>
+        <v>0.2200283982859606</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1756281152017732</v>
+        <v>0.1781713532290372</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6067542100657536</v>
+        <v>0.6018002484850021</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3891365353332803</v>
+        <v>0.3817718501990415</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9405090193826404</v>
+        <v>0.9460820203294296</v>
       </c>
     </row>
     <row r="31">
@@ -1322,22 +1322,22 @@
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6159108801979465</v>
+        <v>0.6172164608636121</v>
       </c>
       <c r="E31" t="n">
-        <v>0.181945614097651</v>
+        <v>0.1839828596059738</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2021435057044025</v>
+        <v>0.1988006795304141</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4137673744935439</v>
+        <v>0.4184157813331981</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9317294853882117</v>
+        <v>0.930448827453537</v>
       </c>
     </row>
     <row r="32">
@@ -1351,22 +1351,22 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2849046614528327</v>
+        <v>0.2872004868277593</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2024397670508006</v>
+        <v>0.2049975912168158</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5126555714963666</v>
+        <v>0.5078019219554248</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2277509100435339</v>
+        <v>0.2206014351276655</v>
       </c>
       <c r="I32" t="n">
-        <v>1.023617493953285</v>
+        <v>1.027294442242523</v>
       </c>
     </row>
     <row r="33">
@@ -1380,22 +1380,22 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5232578872725577</v>
+        <v>0.5250462739927483</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2080495305080608</v>
+        <v>0.2101752072821319</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2686925822193815</v>
+        <v>0.2647785187251198</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2545653050531762</v>
+        <v>0.2602677552676285</v>
       </c>
       <c r="I33" t="n">
-        <v>1.018649919781353</v>
+        <v>1.017959156147486</v>
       </c>
     </row>
     <row r="34">
@@ -1409,22 +1409,22 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3573295880047073</v>
+        <v>0.3598164253657547</v>
       </c>
       <c r="E34" t="n">
-        <v>0.217527150432185</v>
+        <v>0.2197114531301504</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4251432615631078</v>
+        <v>0.4204721215040949</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.06781367355840051</v>
+        <v>0.06065569613834021</v>
       </c>
       <c r="I34" t="n">
-        <v>1.063186885184956</v>
+        <v>1.065037403949264</v>
       </c>
     </row>
     <row r="35">
@@ -1438,22 +1438,22 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4371967093045265</v>
+        <v>0.4393671239128781</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2197052199603339</v>
+        <v>0.2216942620248992</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3430980707351396</v>
+        <v>0.3389386140622227</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09409863856938688</v>
+        <v>0.1004285098506554</v>
       </c>
       <c r="I35" t="n">
-        <v>1.06170605408241</v>
+        <v>1.062026921704069</v>
       </c>
     </row>
     <row r="36">
@@ -1467,22 +1467,22 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.238921060066988</v>
+        <v>0.2412358325515353</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2410744411496037</v>
+        <v>0.2436192601232283</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5200044987834083</v>
+        <v>0.5151449073252364</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2810834387164203</v>
+        <v>0.2739090747737012</v>
       </c>
       <c r="I36" t="n">
-        <v>1.02504930198237</v>
+        <v>1.028758453226218</v>
       </c>
     </row>
     <row r="37">
@@ -1496,22 +1496,22 @@
         <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5303407279799639</v>
+        <v>0.5320723142067497</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2472849567815045</v>
+        <v>0.2493597707852633</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2223743152385315</v>
+        <v>0.218567915007987</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3079664127414323</v>
+        <v>0.3135043991987627</v>
       </c>
       <c r="I37" t="n">
-        <v>1.016186988636728</v>
+        <v>1.014417396532363</v>
       </c>
     </row>
     <row r="38">
@@ -1525,22 +1525,22 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.301454149441904</v>
+        <v>0.3037323461548214</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2637740952370502</v>
+        <v>0.2661502573594665</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4347717553210458</v>
+        <v>0.4301173964857121</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1333176058791418</v>
+        <v>0.1263850503308908</v>
       </c>
       <c r="I38" t="n">
-        <v>1.075142918451594</v>
+        <v>1.077120376529002</v>
       </c>
     </row>
     <row r="39">
@@ -1554,22 +1554,22 @@
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>0.446751137725865</v>
+        <v>0.4488957630771571</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2684841020126569</v>
+        <v>0.2705012804584295</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2847647602614781</v>
+        <v>0.2806029564644134</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1619863774643869</v>
+        <v>0.1682928066127437</v>
       </c>
       <c r="I39" t="n">
-        <v>1.070708832308076</v>
+        <v>1.069818520607082</v>
       </c>
     </row>
     <row r="40">
@@ -1583,22 +1583,22 @@
         <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3703184535157718</v>
+        <v>0.3727503232840589</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2737976041235191</v>
+        <v>0.2757676411673724</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3558839423607091</v>
+        <v>0.3514820355485687</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.01443451115506267</v>
+        <v>0.02126828773549028</v>
       </c>
       <c r="I40" t="n">
-        <v>1.090221220619231</v>
+        <v>1.09059873255322</v>
       </c>
     </row>
     <row r="41">
@@ -1612,22 +1612,22 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2524201534524048</v>
+        <v>0.2546692360353964</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3067703947133809</v>
+        <v>0.3092193006922082</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4408094518342143</v>
+        <v>0.4361114632723954</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1883892983818095</v>
+        <v>0.1814422272369989</v>
       </c>
       <c r="I41" t="n">
-        <v>1.071079582362139</v>
+        <v>1.073176383340442</v>
       </c>
     </row>
     <row r="42">
@@ -1641,22 +1641,22 @@
         <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4525721245504645</v>
+        <v>0.4546793782803824</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3122951201915823</v>
+        <v>0.31422703415401</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2351327552579531</v>
+        <v>0.2310935875656077</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2174393692925114</v>
+        <v>0.2235857907147747</v>
       </c>
       <c r="I42" t="n">
-        <v>1.062633348766715</v>
+        <v>1.06065949673491</v>
       </c>
     </row>
     <row r="43">
@@ -1670,22 +1670,22 @@
         <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>0.311839755529526</v>
+        <v>0.3140546159892492</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3244582943575929</v>
+        <v>0.3266893176804685</v>
       </c>
       <c r="F43" t="n">
-        <v>0.363701950112881</v>
+        <v>0.3592560663302822</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.051862194583355</v>
+        <v>0.04520145034103301</v>
       </c>
       <c r="I43" t="n">
-        <v>1.096441535673218</v>
+        <v>1.096994230065584</v>
       </c>
     </row>
     <row r="44">
@@ -1699,22 +1699,22 @@
         <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3780130190402778</v>
+        <v>0.3804939273308147</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3271246464751758</v>
+        <v>0.3290702096909151</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2948623344845464</v>
+        <v>0.2904358629782702</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08315068455573144</v>
+        <v>0.09005806435254443</v>
       </c>
       <c r="I44" t="n">
-        <v>1.093374443570447</v>
+        <v>1.092508833002762</v>
       </c>
     </row>
     <row r="45">
@@ -1728,22 +1728,22 @@
         <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2605645973177376</v>
+        <v>0.2628489566165471</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3707518728929097</v>
+        <v>0.3729886660412282</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3686835297893527</v>
+        <v>0.3641623773422247</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1081189324716151</v>
+        <v>0.1013134207256776</v>
       </c>
       <c r="I45" t="n">
-        <v>1.086181308950678</v>
+        <v>1.08691711515904</v>
       </c>
     </row>
     <row r="46">
@@ -1757,22 +1757,22 @@
         <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3826791352460478</v>
+        <v>0.3851111843606582</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3744606260441155</v>
+        <v>0.3762215066304926</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2428602387098367</v>
+        <v>0.2386673090088491</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1398188965362111</v>
+        <v>0.1464438753518091</v>
       </c>
       <c r="I46" t="n">
-        <v>1.079119183602584</v>
+        <v>1.077202591727948</v>
       </c>
     </row>
     <row r="47">
@@ -1786,22 +1786,22 @@
         <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3180091237522048</v>
+        <v>0.320251527675651</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3809536872193404</v>
+        <v>0.3831562666396207</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3010371890284548</v>
+        <v>0.2965922056847283</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.01697193472374997</v>
+        <v>0.02365932199092269</v>
       </c>
       <c r="I47" t="n">
-        <v>1.093386593551202</v>
+        <v>1.092697800243577</v>
       </c>
     </row>
     <row r="48">
@@ -1815,22 +1815,22 @@
         <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2654035326422398</v>
+        <v>0.2677020208423134</v>
       </c>
       <c r="E48" t="n">
-        <v>0.429603640722768</v>
+        <v>0.4317934024696367</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3049928266349923</v>
+        <v>0.3005045766880499</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.03958929399275257</v>
+        <v>0.03280255584573649</v>
       </c>
       <c r="I48" t="n">
-        <v>1.077196518879618</v>
+        <v>1.076717253129289</v>
       </c>
     </row>
     <row r="49">
@@ -1844,22 +1844,22 @@
         <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3216410684061963</v>
+        <v>0.3238520246456553</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4306378122745465</v>
+        <v>0.4326276021197292</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2477211193192572</v>
+        <v>0.2435203732346155</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07391994908693902</v>
+        <v>0.08033165141103984</v>
       </c>
       <c r="I49" t="n">
-        <v>1.073333580866863</v>
+        <v>1.071607954427747</v>
       </c>
     </row>
     <row r="50">
@@ -1873,22 +1873,22 @@
         <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2683030534120803</v>
+        <v>0.2705469205608662</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4808897715770156</v>
+        <v>0.4828519992900429</v>
       </c>
       <c r="F50" t="n">
-        <v>0.250807175010904</v>
+        <v>0.246601080149091</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01749587840117628</v>
+        <v>0.02394584041177517</v>
       </c>
       <c r="I50" t="n">
-        <v>1.05194149639525</v>
+        <v>1.050464044792634</v>
       </c>
     </row>
   </sheetData>
